--- a/data/trans_dic/P45C_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,46; 18,07</t>
+          <t>11,18; 17,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,63; 24,58</t>
+          <t>16,72; 24,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,47; 20,53</t>
+          <t>13,03; 20,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,79; 18,59</t>
+          <t>11,58; 18,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,33; 20,73</t>
+          <t>11,97; 20,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,64; 18,0</t>
+          <t>9,83; 17,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,84; 24,81</t>
+          <t>15,62; 24,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 14,52</t>
+          <t>9,07; 14,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,64; 17,8</t>
+          <t>12,45; 17,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,85; 20,38</t>
+          <t>14,75; 20,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,24; 20,76</t>
+          <t>15,31; 20,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,33; 15,78</t>
+          <t>11,35; 15,65</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,61; 20,06</t>
+          <t>12,02; 20,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,61; 18,25</t>
+          <t>10,8; 18,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 15,85</t>
+          <t>8,68; 15,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,76; 20,36</t>
+          <t>12,54; 20,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,81; 20,42</t>
+          <t>12,92; 20,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,78; 21,51</t>
+          <t>12,46; 21,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,72; 21,44</t>
+          <t>12,67; 20,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,91; 18,59</t>
+          <t>12,22; 18,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,38; 18,94</t>
+          <t>13,57; 19,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,9; 18,48</t>
+          <t>12,86; 18,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,58; 16,82</t>
+          <t>11,83; 17,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,18; 18,34</t>
+          <t>12,99; 18,26</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,93; 23,07</t>
+          <t>16,04; 22,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 18,14</t>
+          <t>12,66; 18,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,8; 15,94</t>
+          <t>9,76; 15,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 18,21</t>
+          <t>3,92; 18,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 19,9</t>
+          <t>9,26; 20,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,67; 18,69</t>
+          <t>9,81; 17,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 16,89</t>
+          <t>7,11; 17,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,83; 20,3</t>
+          <t>10,72; 19,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,02; 20,72</t>
+          <t>15,47; 21,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,41; 17,13</t>
+          <t>12,41; 17,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,9</t>
+          <t>9,99; 15,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 17,65</t>
+          <t>4,42; 17,59</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,01; 15,95</t>
+          <t>12,24; 16,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,9; 18,44</t>
+          <t>13,88; 18,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,6; 14,69</t>
+          <t>10,62; 14,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,23; 16,95</t>
+          <t>12,12; 16,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,63; 15,54</t>
+          <t>10,55; 15,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 17,2</t>
+          <t>12,05; 17,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,34; 15,95</t>
+          <t>11,46; 16,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 13,94</t>
+          <t>5,44; 14,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,21; 15,2</t>
+          <t>12,11; 15,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,94; 17,28</t>
+          <t>13,79; 17,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,48; 14,55</t>
+          <t>11,56; 14,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,68; 14,72</t>
+          <t>8,63; 14,79</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,57; 16,84</t>
+          <t>9,75; 17,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,93; 19,29</t>
+          <t>13,07; 19,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,33; 12,68</t>
+          <t>7,23; 12,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,78; 24,03</t>
+          <t>15,6; 23,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 10,96</t>
+          <t>6,2; 10,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,08; 12,71</t>
+          <t>8,1; 12,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 11,86</t>
+          <t>7,66; 11,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,04; 14,78</t>
+          <t>9,04; 14,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,06</t>
+          <t>8,12; 12,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,88; 14,65</t>
+          <t>11,07; 14,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,92; 11,24</t>
+          <t>7,92; 11,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,11; 17,05</t>
+          <t>11,89; 17,03</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,32; 26,58</t>
+          <t>17,56; 27,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,15; 38,76</t>
+          <t>27,36; 38,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,13; 28,31</t>
+          <t>18,47; 28,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,69; 32,26</t>
+          <t>13,64; 32,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,96; 13,65</t>
+          <t>9,97; 13,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,03; 16,13</t>
+          <t>11,93; 16,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,92; 16,13</t>
+          <t>11,82; 16,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,79; 15,56</t>
+          <t>10,67; 15,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,07; 15,47</t>
+          <t>12,04; 15,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15,55; 19,75</t>
+          <t>15,57; 19,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,13; 18,1</t>
+          <t>13,98; 17,95</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,31; 18,34</t>
+          <t>12,34; 18,27</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,47; 16,97</t>
+          <t>14,47; 17,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,28; 18,94</t>
+          <t>16,32; 18,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,18; 14,54</t>
+          <t>12,24; 14,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,48; 17,17</t>
+          <t>12,32; 17,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,36; 13,6</t>
+          <t>11,31; 13,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,32; 14,63</t>
+          <t>12,31; 14,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,42; 14,77</t>
+          <t>12,47; 14,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,97; 13,53</t>
+          <t>9,75; 13,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,29; 14,97</t>
+          <t>13,17; 14,89</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,57; 16,36</t>
+          <t>14,65; 16,4</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,7; 14,33</t>
+          <t>12,73; 14,39</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,84; 14,92</t>
+          <t>11,96; 15,01</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54314; 85611</t>
+          <t>52961; 84487</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72535; 107216</t>
+          <t>72932; 106900</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57301; 87309</t>
+          <t>55406; 88327</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59549; 93918</t>
+          <t>58511; 93078</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>37698; 63353</t>
+          <t>36585; 62850</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30110; 56238</t>
+          <t>30732; 54191</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54132; 84745</t>
+          <t>53379; 82827</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40061; 64963</t>
+          <t>40599; 64417</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>98547; 138761</t>
+          <t>97063; 136891</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>111155; 152589</t>
+          <t>110431; 152541</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116850; 159206</t>
+          <t>117410; 158700</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>107894; 150340</t>
+          <t>108156; 149117</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46285; 73608</t>
+          <t>44097; 73428</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43649; 75100</t>
+          <t>44464; 74763</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33015; 59336</t>
+          <t>32486; 58221</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57719; 92074</t>
+          <t>56722; 92175</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47620; 75943</t>
+          <t>48034; 76491</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42824; 72063</t>
+          <t>41751; 72273</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46911; 79105</t>
+          <t>46735; 75841</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45583; 71116</t>
+          <t>46763; 69489</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>98836; 139899</t>
+          <t>100266; 140961</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96264; 137931</t>
+          <t>96006; 137699</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86055; 125018</t>
+          <t>87905; 126554</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>110049; 153083</t>
+          <t>108415; 152462</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>86091; 124709</t>
+          <t>86720; 122155</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>77548; 113995</t>
+          <t>79579; 117183</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50583; 82313</t>
+          <t>50378; 81034</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24815; 121462</t>
+          <t>26145; 122444</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15759; 33383</t>
+          <t>15528; 33937</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24742; 47824</t>
+          <t>25106; 45649</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11137; 28054</t>
+          <t>11809; 28400</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18009; 33774</t>
+          <t>17835; 33063</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>106363; 146776</t>
+          <t>109601; 150236</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109786; 151517</t>
+          <t>109779; 152892</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67042; 101709</t>
+          <t>68176; 104885</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42458; 147021</t>
+          <t>36852; 146591</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>148392; 196986</t>
+          <t>151243; 199701</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>159367; 211439</t>
+          <t>159075; 209965</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>120683; 167260</t>
+          <t>120901; 166001</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126014; 174630</t>
+          <t>124907; 173361</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>75597; 110478</t>
+          <t>75019; 113209</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>92267; 130981</t>
+          <t>91717; 132920</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93124; 130986</t>
+          <t>94081; 133605</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>56399; 136293</t>
+          <t>53149; 138882</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>237659; 295832</t>
+          <t>235716; 295901</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>266015; 329738</t>
+          <t>263135; 326634</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>224867; 285114</t>
+          <t>226497; 284740</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>174195; 295562</t>
+          <t>173292; 296955</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33443; 58876</t>
+          <t>34081; 59875</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>65646; 97938</t>
+          <t>66348; 98778</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45414; 78603</t>
+          <t>44815; 76084</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74752; 113784</t>
+          <t>73859; 113211</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>35201; 62231</t>
+          <t>35238; 61372</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61266; 96397</t>
+          <t>61420; 95709</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56289; 86915</t>
+          <t>56104; 86701</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>76022; 124288</t>
+          <t>75964; 121508</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>75155; 110694</t>
+          <t>74546; 111202</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>137677; 185411</t>
+          <t>140191; 188112</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>107089; 152093</t>
+          <t>107183; 152496</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>159175; 224068</t>
+          <t>156264; 223764</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>51360; 78811</t>
+          <t>52077; 81080</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71638; 102291</t>
+          <t>72203; 101192</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51215; 79972</t>
+          <t>52168; 80377</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32922; 77587</t>
+          <t>32814; 79032</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>123994; 169945</t>
+          <t>124163; 166369</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>131397; 176189</t>
+          <t>130273; 175523</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>128044; 173340</t>
+          <t>126983; 173099</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>82087; 118381</t>
+          <t>81181; 118671</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>186107; 238471</t>
+          <t>185657; 236303</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>210942; 267852</t>
+          <t>211180; 269028</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>191812; 245686</t>
+          <t>189777; 243552</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>123246; 183622</t>
+          <t>123575; 182911</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>472070; 553581</t>
+          <t>471991; 560085</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>552669; 642735</t>
+          <t>554090; 640850</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>408912; 488168</t>
+          <t>410988; 488731</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>386605; 578485</t>
+          <t>414936; 582146</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>382981; 458309</t>
+          <t>381206; 458407</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>433176; 514325</t>
+          <t>432600; 517127</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>435450; 517757</t>
+          <t>437204; 516017</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>356568; 483595</t>
+          <t>348669; 490315</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>881263; 993088</t>
+          <t>873602; 987858</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1006792; 1130522</t>
+          <t>1012333; 1132855</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>871402; 983072</t>
+          <t>873389; 987299</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>821834; 1036392</t>
+          <t>830190; 1041961</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P45C_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 17,83</t>
+          <t>11,12; 17,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,72; 24,51</t>
+          <t>16,66; 24,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,03; 20,77</t>
+          <t>12,84; 20,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,58; 18,42</t>
+          <t>13,13; 20,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,97; 20,56</t>
+          <t>12,3; 20,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 17,34</t>
+          <t>9,86; 17,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,62; 24,24</t>
+          <t>15,7; 24,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,07; 14,4</t>
+          <t>9,08; 14,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,45; 17,56</t>
+          <t>12,49; 17,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,75; 20,37</t>
+          <t>14,86; 20,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,31; 20,69</t>
+          <t>15,33; 20,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,35; 15,65</t>
+          <t>11,81; 16,12</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,02; 20,01</t>
+          <t>12,44; 20,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,8; 18,17</t>
+          <t>10,82; 18,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,68; 15,55</t>
+          <t>9,16; 16,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,54; 20,38</t>
+          <t>12,79; 19,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,92; 20,57</t>
+          <t>12,94; 19,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,46; 21,57</t>
+          <t>12,64; 21,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,67; 20,56</t>
+          <t>12,69; 20,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,22; 18,16</t>
+          <t>12,16; 17,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,57; 19,08</t>
+          <t>13,44; 18,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,86; 18,45</t>
+          <t>12,64; 18,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,83; 17,03</t>
+          <t>11,64; 17,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,99; 18,26</t>
+          <t>13,36; 18,25</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,04; 22,6</t>
+          <t>15,85; 22,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,66; 18,65</t>
+          <t>12,36; 18,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 15,69</t>
+          <t>9,61; 15,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 18,36</t>
+          <t>14,26; 21,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,26; 20,23</t>
+          <t>9,24; 19,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 17,84</t>
+          <t>9,75; 18,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 17,1</t>
+          <t>7,06; 17,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,72; 19,87</t>
+          <t>10,83; 20,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,47; 21,21</t>
+          <t>15,31; 20,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,41; 17,29</t>
+          <t>12,4; 17,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,99; 15,37</t>
+          <t>9,87; 15,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 17,59</t>
+          <t>13,99; 20,06</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,24; 16,17</t>
+          <t>12,15; 16,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,88; 18,32</t>
+          <t>13,92; 18,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 14,58</t>
+          <t>10,71; 14,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 16,82</t>
+          <t>12,97; 17,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,55; 15,92</t>
+          <t>10,61; 15,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,05; 17,46</t>
+          <t>12,13; 17,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,46; 16,27</t>
+          <t>11,33; 16,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,44; 14,21</t>
+          <t>11,35; 15,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,11; 15,2</t>
+          <t>12,13; 15,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,79; 17,12</t>
+          <t>13,79; 17,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 14,53</t>
+          <t>11,51; 14,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,63; 14,79</t>
+          <t>12,82; 16,08</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,75; 17,13</t>
+          <t>9,67; 17,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,07; 19,45</t>
+          <t>13,04; 19,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,28</t>
+          <t>7,32; 12,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,6; 23,91</t>
+          <t>15,53; 23,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 10,8</t>
+          <t>6,12; 10,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 12,62</t>
+          <t>8,12; 12,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,66; 11,83</t>
+          <t>7,36; 11,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,04; 14,45</t>
+          <t>11,61; 15,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 12,12</t>
+          <t>8,34; 12,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,07; 14,86</t>
+          <t>10,87; 14,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,92; 11,27</t>
+          <t>8,12; 11,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,89; 17,03</t>
+          <t>13,92; 18,07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,56; 27,35</t>
+          <t>17,6; 26,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,36; 38,35</t>
+          <t>27,69; 38,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,47; 28,45</t>
+          <t>18,37; 28,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,64; 32,86</t>
+          <t>14,19; 32,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,97; 13,36</t>
+          <t>10,19; 13,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,93; 16,07</t>
+          <t>11,98; 16,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,82; 16,11</t>
+          <t>11,99; 16,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,67; 15,6</t>
+          <t>10,39; 15,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,04; 15,32</t>
+          <t>12,05; 15,38</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15,57; 19,84</t>
+          <t>15,83; 19,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,98; 17,95</t>
+          <t>14,1; 18,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,34; 18,27</t>
+          <t>12,11; 17,64</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,47; 17,17</t>
+          <t>14,45; 17,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,32; 18,88</t>
+          <t>16,28; 18,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,24; 14,56</t>
+          <t>12,25; 14,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,32; 17,28</t>
+          <t>15,5; 18,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,31; 13,6</t>
+          <t>11,38; 13,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,31; 14,71</t>
+          <t>12,39; 14,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,47; 14,72</t>
+          <t>12,47; 14,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,75; 13,71</t>
+          <t>12,09; 14,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,17; 14,89</t>
+          <t>13,29; 14,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 16,4</t>
+          <t>14,62; 16,39</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,73; 14,39</t>
+          <t>12,65; 14,32</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,96; 15,01</t>
+          <t>14,1; 15,91</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75317</t>
+          <t>88214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>52240</t>
+          <t>56367</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>127557</t>
+          <t>144582</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52961; 84487</t>
+          <t>52686; 84546</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72932; 106900</t>
+          <t>72671; 108403</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55406; 88327</t>
+          <t>54609; 86599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58511; 93078</t>
+          <t>72319; 110554</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36585; 62850</t>
+          <t>37594; 63085</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30732; 54191</t>
+          <t>30815; 54223</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53379; 82827</t>
+          <t>53642; 84097</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40599; 64417</t>
+          <t>44342; 69357</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>97063; 136891</t>
+          <t>97319; 138071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110431; 152541</t>
+          <t>111235; 152248</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117410; 158700</t>
+          <t>117541; 160921</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>108156; 149117</t>
+          <t>122676; 167448</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73311</t>
+          <t>78099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57099</t>
+          <t>62477</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>130410</t>
+          <t>140576</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44097; 73428</t>
+          <t>45664; 73994</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44464; 74763</t>
+          <t>44542; 76867</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32486; 58221</t>
+          <t>34267; 60626</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56722; 92175</t>
+          <t>61810; 96364</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48034; 76491</t>
+          <t>48112; 73620</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41751; 72273</t>
+          <t>42333; 72816</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46735; 75841</t>
+          <t>46829; 75082</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46763; 69489</t>
+          <t>51443; 75863</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100266; 140961</t>
+          <t>99282; 139330</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96006; 137699</t>
+          <t>94373; 135893</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87905; 126554</t>
+          <t>86498; 126679</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>108415; 152462</t>
+          <t>121121; 165447</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72880</t>
+          <t>82962</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>27844</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97673</t>
+          <t>110806</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>86720; 122155</t>
+          <t>85663; 123866</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>79579; 117183</t>
+          <t>77709; 114174</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50378; 81034</t>
+          <t>49628; 81587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26145; 122444</t>
+          <t>67040; 101578</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15528; 33937</t>
+          <t>15508; 33477</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25106; 45649</t>
+          <t>24943; 46435</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11809; 28400</t>
+          <t>11721; 28567</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17835; 33063</t>
+          <t>20232; 37485</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>109601; 150236</t>
+          <t>108410; 148304</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109779; 152892</t>
+          <t>109676; 152444</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68176; 104885</t>
+          <t>67381; 103035</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36852; 146591</t>
+          <t>91929; 131794</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148905</t>
+          <t>170472</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>103016</t>
+          <t>115449</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>251921</t>
+          <t>285921</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>151243; 199701</t>
+          <t>150115; 199631</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>159075; 209965</t>
+          <t>159593; 211619</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>120901; 166001</t>
+          <t>121950; 167051</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>124907; 173361</t>
+          <t>146218; 199026</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>75019; 113209</t>
+          <t>75448; 111105</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>91717; 132920</t>
+          <t>92352; 132591</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>94081; 133605</t>
+          <t>93058; 134124</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53149; 138882</t>
+          <t>97681; 135896</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>235716; 295901</t>
+          <t>236068; 295811</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>263135; 326634</t>
+          <t>263046; 326104</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>226497; 284740</t>
+          <t>225557; 282699</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>173292; 296955</t>
+          <t>254905; 319564</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92873</t>
+          <t>107993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>101234</t>
+          <t>112325</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>194106</t>
+          <t>220319</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34081; 59875</t>
+          <t>33802; 60789</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>66348; 98778</t>
+          <t>66188; 97682</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44815; 76084</t>
+          <t>45351; 76579</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73859; 113211</t>
+          <t>87979; 130933</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>35238; 61372</t>
+          <t>34773; 61059</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61420; 95709</t>
+          <t>61552; 97973</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56104; 86701</t>
+          <t>53925; 86301</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>75964; 121508</t>
+          <t>96403; 129738</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>74546; 111202</t>
+          <t>76547; 111868</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>140191; 188112</t>
+          <t>137628; 185372</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>107183; 152496</t>
+          <t>109806; 152266</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>156264; 223764</t>
+          <t>194410; 252325</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>52990</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>99502</t>
+          <t>106245</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>150518</t>
+          <t>159235</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52077; 81080</t>
+          <t>52175; 79972</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72203; 101192</t>
+          <t>73080; 102074</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52168; 80377</t>
+          <t>51894; 80822</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32814; 79032</t>
+          <t>33654; 77783</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>124163; 166369</t>
+          <t>126948; 169037</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>130273; 175523</t>
+          <t>130898; 175790</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>126983; 173099</t>
+          <t>128876; 175089</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>81181; 118671</t>
+          <t>87699; 126954</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>185657; 236303</t>
+          <t>185857; 237158</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>211180; 269028</t>
+          <t>214642; 269447</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>189777; 243552</t>
+          <t>191337; 244278</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>123575; 182911</t>
+          <t>130847; 190711</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>514301</t>
+          <t>580732</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>437885</t>
+          <t>480708</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>952186</t>
+          <t>1061439</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>471991; 560085</t>
+          <t>471571; 555106</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>554090; 640850</t>
+          <t>552603; 643051</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>410988; 488731</t>
+          <t>411139; 490971</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>414936; 582146</t>
+          <t>532252; 631501</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>381206; 458407</t>
+          <t>383512; 458242</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>432600; 517127</t>
+          <t>435502; 514561</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>437204; 516017</t>
+          <t>437246; 519968</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>348669; 490315</t>
+          <t>439130; 521032</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>873602; 987858</t>
+          <t>881155; 990373</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1012333; 1132855</t>
+          <t>1010035; 1132651</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>873389; 987299</t>
+          <t>868154; 982395</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>830190; 1041961</t>
+          <t>996245; 1124306</t>
         </is>
       </c>
     </row>
